--- a/AI Audit Log_VoPhamMy.xlsx
+++ b/AI Audit Log_VoPhamMy.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_IT\Semester\SU26\SE20C02_LAB211_SU26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7.SU26\SWD392\AI_Audit_Log\ai-audit-log-vophammy24\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DB4BAFD-22E4-4A56-8BB6-7291655F4E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BC4B3B-A9A1-4729-8AEB-5E1C04614BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 2" sheetId="6" r:id="rId2"/>
+    <sheet name="Assignment 1" sheetId="2" r:id="rId3"/>
+    <sheet name="Assignment 2" sheetId="3" r:id="rId4"/>
+    <sheet name="Assignment 3" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,19 +31,14 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -95,12 +91,29 @@
     <t>Phản hồi: AI tóm tắt 5 papers với tên tác giả, năm xuất bản và tóm tắt nội dung.
 Kiểm chứng: Tìm trên Google Scholar: 2/5 papers AI nêu là không tồn tại (fabrication). Tôi đã thay bằng 2 papers mà tôi đã tìm kiếm trên research gates và đã kiểm chứng trên google scholar.</t>
   </si>
+  <si>
+    <t>Tôi cần vẽ Use Case Diagram cho Hệ thống quản lý thực phẩm dựa theo các actor như User, Admin, Scanning Service, AI, Notification Service, External Video Platform. Hãy cho tôi biết vẽ Use Case Diagram theo các actor hay các tính năng chính sẽ phù hợp với Hệ thống này.</t>
+  </si>
+  <si>
+    <t>Phản hồi: Đưa ra cách phù hợp là vẽ theo cấu trúc, đưa ra khó khăn khi vẽ dựa trên actor. 
+Quyết định: Chọn cách vẽ dựa trên actor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nếu tôi không chọn vẽ use case theo từng feature mà vẽ theo actor thì nên làm gì để đảm bảo nó vẫn đáp ưng yêu cầu chung cho một bản report, vẫn đảm bảo người xem có thể hiểu được các chức năng của hệ thống.  </t>
+  </si>
+  <si>
+    <t>Phản hồi: Đưa ra 4 yêu cầu cần thiết khi vẽ use case dựa vào actor.
+Quyết định: Dựa trên 4 yêu cầu đã đưa ra và vẽ use case diagram đáp ứng yêu cầu.</t>
+  </si>
+  <si>
+    <t>Abstraction</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +130,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -126,7 +152,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -149,11 +175,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -171,6 +219,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -508,15 +595,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.9296875" customWidth="1"/>
-    <col min="2" max="2" width="26.86328125" customWidth="1"/>
-    <col min="3" max="3" width="24.265625" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
     <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -531,7 +618,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -545,7 +632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -559,7 +646,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -573,7 +660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -593,27 +680,98 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BDAC948-6289-4C41-B8C5-2E7AC42CB74A}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.5546875" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="4" max="4" width="63" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
